--- a/src/main/resources/excel/3 - Phrasal Verb.xlsx
+++ b/src/main/resources/excel/3 - Phrasal Verb.xlsx
@@ -21719,7 +21719,7 @@
   <dimension ref="A1:F525"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="53.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="85.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="71.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="58.64"/>
